--- a/backend/data/financials_by_company/0865.HK.xlsx
+++ b/backend/data/financials_by_company/0865.HK.xlsx
@@ -4084,7 +4084,7 @@
         <v>-7050000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
         <v>-0.0015799999</v>
